--- a/artfynd/A 10666-2026 artfynd.xlsx
+++ b/artfynd/A 10666-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY3"/>
+  <dimension ref="A1:AY7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,15 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>122763398</v>
+        <v>122763401</v>
       </c>
       <c r="B2" t="n">
-        <v>98391</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80461</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -691,21 +686,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>221952</v>
+        <v>6462</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>747686</v>
+        <v>747459</v>
       </c>
       <c r="R2" t="n">
-        <v>7452494</v>
+        <v>7452542</v>
       </c>
       <c r="S2" t="n">
         <v>25</v>
@@ -777,15 +772,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122763382</v>
+        <v>122763402</v>
       </c>
       <c r="B3" t="n">
-        <v>98391</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>106229</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -793,21 +783,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>221952</v>
+        <v>221725</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Ögonpyrola</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Moneses uniflora</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(L.) A. Gray</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -817,10 +807,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>747793</v>
+        <v>747442</v>
       </c>
       <c r="R3" t="n">
-        <v>7452340</v>
+        <v>7452562</v>
       </c>
       <c r="S3" t="n">
         <v>25</v>
@@ -876,6 +866,394 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>122763398</v>
+      </c>
+      <c r="B4" t="n">
+        <v>99140</v>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E4" t="n">
+        <v>221952</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Spindelblomster</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Neottia cordata</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>(L.) Rich.</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>Gällivare kn, Lu lm</t>
+        </is>
+      </c>
+      <c r="Q4" t="n">
+        <v>747686</v>
+      </c>
+      <c r="R4" t="n">
+        <v>7452494</v>
+      </c>
+      <c r="S4" t="n">
+        <v>25</v>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>Gällivare</t>
+        </is>
+      </c>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>Lule lappmark</t>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>Gällivare</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>2024-07-04</t>
+        </is>
+      </c>
+      <c r="AA4" t="inlineStr">
+        <is>
+          <t>2024-07-04</t>
+        </is>
+      </c>
+      <c r="AD4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT4" t="inlineStr"/>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>Otilia Johansson</t>
+        </is>
+      </c>
+      <c r="AX4" t="inlineStr">
+        <is>
+          <t>Otilia Johansson</t>
+        </is>
+      </c>
+      <c r="AY4" t="inlineStr"/>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>122763400</v>
+      </c>
+      <c r="B5" t="n">
+        <v>99140</v>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>221952</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Spindelblomster</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Neottia cordata</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>(L.) Rich.</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>Gällivare kn, Lu lm</t>
+        </is>
+      </c>
+      <c r="Q5" t="n">
+        <v>747455</v>
+      </c>
+      <c r="R5" t="n">
+        <v>7452542</v>
+      </c>
+      <c r="S5" t="n">
+        <v>25</v>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>Gällivare</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>Lule lappmark</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>Gällivare</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>2024-07-04</t>
+        </is>
+      </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>2024-07-04</t>
+        </is>
+      </c>
+      <c r="AD5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT5" t="inlineStr"/>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>Otilia Johansson</t>
+        </is>
+      </c>
+      <c r="AX5" t="inlineStr">
+        <is>
+          <t>Otilia Johansson</t>
+        </is>
+      </c>
+      <c r="AY5" t="inlineStr"/>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>122763403</v>
+      </c>
+      <c r="B6" t="n">
+        <v>99140</v>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>221952</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Spindelblomster</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Neottia cordata</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>(L.) Rich.</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>Gällivare kn, Lu lm</t>
+        </is>
+      </c>
+      <c r="Q6" t="n">
+        <v>747375</v>
+      </c>
+      <c r="R6" t="n">
+        <v>7452903</v>
+      </c>
+      <c r="S6" t="n">
+        <v>25</v>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>Gällivare</t>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>Lule lappmark</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>Gällivare</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>2024-07-04</t>
+        </is>
+      </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>2024-07-04</t>
+        </is>
+      </c>
+      <c r="AD6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT6" t="inlineStr"/>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>Otilia Johansson</t>
+        </is>
+      </c>
+      <c r="AX6" t="inlineStr">
+        <is>
+          <t>Otilia Johansson</t>
+        </is>
+      </c>
+      <c r="AY6" t="inlineStr"/>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>122763382</v>
+      </c>
+      <c r="B7" t="n">
+        <v>99140</v>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>221952</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Spindelblomster</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Neottia cordata</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>(L.) Rich.</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>Gällivare kn, Lu lm</t>
+        </is>
+      </c>
+      <c r="Q7" t="n">
+        <v>747793</v>
+      </c>
+      <c r="R7" t="n">
+        <v>7452340</v>
+      </c>
+      <c r="S7" t="n">
+        <v>25</v>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>Gällivare</t>
+        </is>
+      </c>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>Lule lappmark</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>Gällivare</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>2024-07-04</t>
+        </is>
+      </c>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t>2024-07-04</t>
+        </is>
+      </c>
+      <c r="AD7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT7" t="inlineStr"/>
+      <c r="AW7" t="inlineStr">
+        <is>
+          <t>Otilia Johansson</t>
+        </is>
+      </c>
+      <c r="AX7" t="inlineStr">
+        <is>
+          <t>Otilia Johansson</t>
+        </is>
+      </c>
+      <c r="AY7" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 10666-2026 artfynd.xlsx
+++ b/artfynd/A 10666-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY7"/>
+  <dimension ref="A1:AZ7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -769,6 +774,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122763401</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -866,6 +876,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122763402</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -963,6 +978,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122763398</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1060,6 +1080,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122763400</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1157,6 +1182,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122763403</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1254,8 +1284,21 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122763382</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>